--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/2DO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXIII/LTAIPT_A63F33.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/2DO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXIII/LTAIPT_A63F33.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="495" windowWidth="19815" windowHeight="9405"/>
+    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="8385"/>
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="95">
   <si>
     <t>48989</t>
   </si>
@@ -187,28 +187,55 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>31/12/2022</t>
+    <t>2023</t>
   </si>
   <si>
     <t>De concertación con el sector social</t>
   </si>
   <si>
+    <t>Condiciones Generales de Trabajo del Sindicato de Trabajdores Administrativos y de Intendencia del Colegio de Bachilleres del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>11/08/2021</t>
+  </si>
+  <si>
+    <t>Dirección General, Dirección Administrativa y Subdirección Jurídica</t>
+  </si>
+  <si>
+    <t>Regular las relaciones laborales entre el Colegio de Bachilleres del Estado de Tlaxcala  y los trabajadores administrativos y de intendencia.</t>
+  </si>
+  <si>
+    <t>Público- Estatal</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>01/01/2022</t>
+  </si>
+  <si>
+    <t>31/12/2023</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/Condiciones%20Generales%20de%20Trabajo%20STAICOBAT/CONDICIONES%20GRALES%20DE%20TRABAJO%20STAI%202021-2022.pdf</t>
+  </si>
+  <si>
+    <t>Subdirección Jurídica.</t>
+  </si>
+  <si>
     <t>Contrato Colectivo de Trabajo del Sindicato de Trabajadores Académicos del Colegio de Bachilleres del Estado de Tlaxcala</t>
   </si>
   <si>
     <t>02/09/2020</t>
   </si>
   <si>
-    <t>Dirección General, Dirección Administrativa y Subdirección Jurídica</t>
-  </si>
-  <si>
-    <t>4824719</t>
-  </si>
-  <si>
-    <t/>
+    <t>Regular las relaciones laborales entre el Colegio de Bachilleres del Estado de Tlaxcala y los trabajadores académicos.</t>
+  </si>
+  <si>
+    <t>01/02/2021</t>
+  </si>
+  <si>
+    <t>01/02/2023</t>
   </si>
   <si>
     <t>01/02/2020</t>
@@ -217,67 +244,25 @@
     <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202020/Subdireccion%20Juridica/3er_Trimestre/Contrato_Coletivo_de_Trabajo.pdf</t>
   </si>
   <si>
-    <t>Condiciones Generales de Trabajo del Sindicato de Trabajdores Administrativos y de Intendencia del Colegio de Bachilleres del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>11/08/2021</t>
-  </si>
-  <si>
-    <t>4824718</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/Condiciones%20Generales%20de%20Trabajo%20STAICOBAT/CONDICIONES%20GRALES%20DE%20TRABAJO%20STAI%202021-2022.pdf</t>
-  </si>
-  <si>
-    <t>4331183</t>
-  </si>
-  <si>
-    <t>Regular las relaciones laborales entre el Colegio de Bachilleres del Estado de Tlaxcala y los trabajadores académicos</t>
-  </si>
-  <si>
-    <t>público estatal</t>
-  </si>
-  <si>
-    <t>01/02/2022</t>
-  </si>
-  <si>
-    <t>Subdirección Jurídica</t>
-  </si>
-  <si>
-    <t>4331182</t>
-  </si>
-  <si>
-    <t>Regular las relaciones laborales entre el Colegio de Bachilleres del Estado de Tlaxcala  y los trabajadores administrativos y de intendencia</t>
-  </si>
-  <si>
-    <t>01/01/2021</t>
-  </si>
-  <si>
-    <t>F5995EB05F12C2C36AF8AC80DA2F56BC</t>
-  </si>
-  <si>
-    <t>01/04/2022</t>
-  </si>
-  <si>
-    <t>30/06/2022</t>
-  </si>
-  <si>
-    <t>2794406</t>
-  </si>
-  <si>
-    <t>04/07/2022</t>
-  </si>
-  <si>
-    <t>936BEA47AADD63EBD5DC552DA635B33F</t>
-  </si>
-  <si>
-    <t>2794405</t>
-  </si>
-  <si>
-    <t>2743241</t>
-  </si>
-  <si>
-    <t>2743242</t>
+    <t>436123BCE7FDF3ECD677BC33D599C84A</t>
+  </si>
+  <si>
+    <t>01/04/2023</t>
+  </si>
+  <si>
+    <t>30/06/2023</t>
+  </si>
+  <si>
+    <t>8101976</t>
+  </si>
+  <si>
+    <t>26/07/2023</t>
+  </si>
+  <si>
+    <t>2D08626EB6016289FE0ADEB8D8DD6642</t>
+  </si>
+  <si>
+    <t>8101975</t>
   </si>
   <si>
     <t>De coordinación con el sector privado</t>
@@ -320,54 +305,6 @@
   </si>
   <si>
     <t>Denominación o razón social con quien se celebra</t>
-  </si>
-  <si>
-    <t>F5EDCA6ECF70852CA483725AC344F429</t>
-  </si>
-  <si>
-    <t>Héctor Fernando</t>
-  </si>
-  <si>
-    <t>Lima</t>
-  </si>
-  <si>
-    <t>Hernández</t>
-  </si>
-  <si>
-    <t>Sindicato de Trabajadores Academicos del Colegio de Bachilleres del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>F5EDCA6ECF70852C81FA5E085EEFB3E8</t>
-  </si>
-  <si>
-    <t>Juan</t>
-  </si>
-  <si>
-    <t>Netzahuatl</t>
-  </si>
-  <si>
-    <t>Saldaña</t>
-  </si>
-  <si>
-    <t>Sindicato de Trabajadores Admnistrativos y de Intendecia del Colegio de Bachilleres del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>822FF20A3EDE9D50825571703DFDB335</t>
-  </si>
-  <si>
-    <t>4641CC1B93322EA44D85ADB694D96404</t>
-  </si>
-  <si>
-    <t>24B8CCA20B37960E206A171575A42402</t>
-  </si>
-  <si>
-    <t>6D1B42D9C591A3A0584C0CCD5B19D436</t>
-  </si>
-  <si>
-    <t>DC7C87290AC0724777BA0734B8B80506</t>
-  </si>
-  <si>
-    <t>FA98D80914B8F56C9041F6CBE27980D8</t>
   </si>
 </sst>
 </file>
@@ -766,7 +703,7 @@
   <dimension ref="A1:U9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.85546875" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="36.140625" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
@@ -1038,64 +975,64 @@
     </row>
     <row r="8" spans="1:21" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>55</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="G8" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H8" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>60</v>
-      </c>
       <c r="I8" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="L8" s="3" t="s">
         <v>62</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="N8" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="O8" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>63</v>
-      </c>
       <c r="P8" s="3" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="T8" s="3" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="U8" s="3" t="s">
         <v>62</v>
@@ -1103,64 +1040,64 @@
     </row>
     <row r="9" spans="1:21" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>55</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E9" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>65</v>
-      </c>
       <c r="G9" s="3" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="H9" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="J9" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>75</v>
-      </c>
       <c r="K9" s="3" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="L9" s="3" t="s">
         <v>62</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="O9" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="R9" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q9" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="R9" s="3" t="s">
-        <v>73</v>
-      </c>
       <c r="S9" s="3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="T9" s="3" t="s">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="U9" s="3" t="s">
         <v>62</v>
@@ -1177,7 +1114,7 @@
     <mergeCell ref="G3:I3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E195">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E199">
       <formula1>Hidden_14</formula1>
     </dataValidation>
   </dataValidations>
@@ -1192,32 +1129,32 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -1227,15 +1164,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="46.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="51.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="53.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="90.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="52.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -1254,194 +1189,34 @@
     </row>
     <row r="2" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D2" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E2" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="F2" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
